--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Maria Berdén Evertsson, Bengt Evertsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Bengt Evertsson</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,68 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135024708</v>
+        <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>57167</v>
+        <v>93379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Bäcktorp, Vstm</t>
+          <t>Hoas berg, Hoas berg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496546</v>
+        <v>496571</v>
       </c>
       <c r="R2" t="n">
-        <v>6625651</v>
+        <v>6625747</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Såg fjäder från tjäderhönan.</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,58 +771,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135024708</t>
+          <t>https://artportalen.se/Sighting/135887168</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135024946</v>
+        <v>135792232</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,35 +825,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Bäcktorp2, Vstm</t>
+          <t>Hoas berg, Hoas berg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496456</v>
+        <v>496563</v>
       </c>
       <c r="R3" t="n">
-        <v>6625847</v>
+        <v>6625613</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,12 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,18 +886,2176 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135792232</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135789569</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>496475</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6625763</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135789569</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135791393</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>496477</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6625767</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791393</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135791636</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>496563</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6625613</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791636</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135886992</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496583</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6625823</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886992</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135024708</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norra Bäcktorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496546</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6625651</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Såg fjäder från tjäderhönan.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Evertsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135024708</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135024946</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norra Bäcktorp2, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496456</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6625847</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bengt Evertsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135024946</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135886531</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496562</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6625652</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886531</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135887046</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496574</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6625744</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887046</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135887064</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496583</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6625744</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887064</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135887216</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496571</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6625747</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887216</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135791443</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57781</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496477</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6625767</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spelflykt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791443</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135789400</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496475</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6625763</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kallar 80 ggr.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135789400</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135791227</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496551</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6625632</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kallar 30 ggr.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791227</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135789509</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57801</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496475</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6625763</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135789509</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135789458</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496475</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6625763</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Noteras flera ggr under dagen. Stationär.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135789458</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135791553</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496551</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6625623</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spel/sång och varnande flera ggr under dagen.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791553</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135789618</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496475</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6625763</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Noterad flera gånger under dagen.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135789618</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135791712</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hoas berg, Hoas berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496563</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6625613</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Noterad flera gånger under dagen.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791712</t>
         </is>
       </c>
     </row>
@@ -936,6 +3063,24 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93379</v>
+        <v>93381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93381</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135792232</v>
       </c>
       <c r="B3" t="n">
-        <v>57901</v>
+        <v>57903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135789569</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135791393</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135791636</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135886992</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135886531</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>135887046</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135887064</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135887216</v>
       </c>
       <c r="B13" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135791443</v>
       </c>
       <c r="B14" t="n">
-        <v>57781</v>
+        <v>57783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135789400</v>
       </c>
       <c r="B15" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135791227</v>
       </c>
       <c r="B16" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135789509</v>
       </c>
       <c r="B17" t="n">
-        <v>57801</v>
+        <v>57803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135789458</v>
       </c>
       <c r="B18" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135791553</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135789618</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135791712</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93398</v>
+        <v>93399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135792232</v>
       </c>
       <c r="B3" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135789569</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135791393</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135791636</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135886992</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135886531</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>135887046</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135887064</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135887216</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135791443</v>
       </c>
       <c r="B14" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135789400</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135791227</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135789509</v>
       </c>
       <c r="B17" t="n">
-        <v>57803</v>
+        <v>57804</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135789458</v>
       </c>
       <c r="B18" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135791553</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135789618</v>
       </c>
       <c r="B20" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135791712</v>
       </c>
       <c r="B21" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93399</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135792232</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135789569</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135791393</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135791636</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135886992</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135886531</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>135887046</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135887064</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135887216</v>
       </c>
       <c r="B13" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135791443</v>
       </c>
       <c r="B14" t="n">
-        <v>57784</v>
+        <v>57788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135789400</v>
       </c>
       <c r="B15" t="n">
-        <v>57824</v>
+        <v>57828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135791227</v>
       </c>
       <c r="B16" t="n">
-        <v>57824</v>
+        <v>57828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135789509</v>
       </c>
       <c r="B17" t="n">
-        <v>57804</v>
+        <v>57808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135789458</v>
       </c>
       <c r="B18" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135791553</v>
       </c>
       <c r="B19" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135789618</v>
       </c>
       <c r="B20" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135791712</v>
       </c>
       <c r="B21" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>93406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135792232</v>
       </c>
       <c r="B3" t="n">
-        <v>57908</v>
+        <v>57909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135789569</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135791393</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135791636</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135886992</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135886531</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>135887046</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135887064</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135887216</v>
       </c>
       <c r="B13" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135791443</v>
       </c>
       <c r="B14" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135789400</v>
       </c>
       <c r="B15" t="n">
-        <v>57828</v>
+        <v>57829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135791227</v>
       </c>
       <c r="B16" t="n">
-        <v>57828</v>
+        <v>57829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135789509</v>
       </c>
       <c r="B17" t="n">
-        <v>57808</v>
+        <v>57809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135789458</v>
       </c>
       <c r="B18" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135791553</v>
       </c>
       <c r="B19" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135789618</v>
       </c>
       <c r="B20" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135791712</v>
       </c>
       <c r="B21" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93406</v>
+        <v>93412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93412</v>
+        <v>93419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135792232</v>
       </c>
       <c r="B3" t="n">
-        <v>57909</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135789569</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135791393</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135791636</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135886992</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135886531</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>135887046</v>
       </c>
       <c r="B11" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135887064</v>
       </c>
       <c r="B12" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135887216</v>
       </c>
       <c r="B13" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135791443</v>
       </c>
       <c r="B14" t="n">
-        <v>57789</v>
+        <v>57794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135789400</v>
       </c>
       <c r="B15" t="n">
-        <v>57829</v>
+        <v>57834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135791227</v>
       </c>
       <c r="B16" t="n">
-        <v>57829</v>
+        <v>57834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135789509</v>
       </c>
       <c r="B17" t="n">
-        <v>57809</v>
+        <v>57814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135789458</v>
       </c>
       <c r="B18" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>135791553</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>135789618</v>
       </c>
       <c r="B20" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135791712</v>
       </c>
       <c r="B21" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135886992</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135886531</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>135887046</v>
       </c>
       <c r="B11" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135887064</v>
       </c>
       <c r="B12" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135887216</v>
       </c>
       <c r="B13" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29409-2026 artfynd.xlsx
+++ b/artfynd/A 29409-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887168</v>
       </c>
       <c r="B2" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
